--- a/artfynd/A 4079-2021 artfynd.xlsx
+++ b/artfynd/A 4079-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 4079-2021 artfynd.xlsx
+++ b/artfynd/A 4079-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY97"/>
+  <dimension ref="A1:AY98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12337,6 +12337,127 @@
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>120271955</v>
+      </c>
+      <c r="B98" t="n">
+        <v>57329</v>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>102977</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Gröngöling</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Picus viridis</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>Högbergsgruvan, Nrk</t>
+        </is>
+      </c>
+      <c r="Q98" t="n">
+        <v>486387</v>
+      </c>
+      <c r="R98" t="n">
+        <v>6565530</v>
+      </c>
+      <c r="S98" t="n">
+        <v>20</v>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>Lekeberg</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>Knista</t>
+        </is>
+      </c>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>2024-10-07</t>
+        </is>
+      </c>
+      <c r="Z98" t="inlineStr">
+        <is>
+          <t>16:54</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>2024-10-07</t>
+        </is>
+      </c>
+      <c r="AB98" t="inlineStr">
+        <is>
+          <t>16:54</t>
+        </is>
+      </c>
+      <c r="AD98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT98" t="inlineStr"/>
+      <c r="AW98" t="inlineStr">
+        <is>
+          <t>Sara Johansson</t>
+        </is>
+      </c>
+      <c r="AX98" t="inlineStr">
+        <is>
+          <t>Sara Johansson</t>
+        </is>
+      </c>
+      <c r="AY98" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 4079-2021 artfynd.xlsx
+++ b/artfynd/A 4079-2021 artfynd.xlsx
@@ -12342,7 +12342,7 @@
         <v>120271955</v>
       </c>
       <c r="B98" t="n">
-        <v>57329</v>
+        <v>57339</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>

--- a/artfynd/A 4079-2021 artfynd.xlsx
+++ b/artfynd/A 4079-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY98"/>
+  <dimension ref="A1:AY99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12458,6 +12458,123 @@
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>121599170</v>
+      </c>
+      <c r="B99" t="n">
+        <v>56568</v>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>Ingridagruvorna, Nrk</t>
+        </is>
+      </c>
+      <c r="Q99" t="n">
+        <v>486219</v>
+      </c>
+      <c r="R99" t="n">
+        <v>6565582</v>
+      </c>
+      <c r="S99" t="n">
+        <v>25</v>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>Lekeberg</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>Knista</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>2024-12-14</t>
+        </is>
+      </c>
+      <c r="Z99" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>2024-12-14</t>
+        </is>
+      </c>
+      <c r="AB99" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>Tjäderspillning</t>
+        </is>
+      </c>
+      <c r="AD99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT99" t="inlineStr"/>
+      <c r="AW99" t="inlineStr">
+        <is>
+          <t>Sara Johansson</t>
+        </is>
+      </c>
+      <c r="AX99" t="inlineStr">
+        <is>
+          <t>Sara Johansson</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 4079-2021 artfynd.xlsx
+++ b/artfynd/A 4079-2021 artfynd.xlsx
@@ -12463,7 +12463,7 @@
         <v>121599170</v>
       </c>
       <c r="B99" t="n">
-        <v>56568</v>
+        <v>56569</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>

--- a/artfynd/A 4079-2021 artfynd.xlsx
+++ b/artfynd/A 4079-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY99"/>
+  <dimension ref="A1:AY100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12463,7 +12463,7 @@
         <v>121599170</v>
       </c>
       <c r="B99" t="n">
-        <v>56569</v>
+        <v>56577</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -12574,6 +12574,123 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>122030502</v>
+      </c>
+      <c r="B100" t="n">
+        <v>56577</v>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>Ribbohyttan Rosenborg, Lekeberg, Nrk</t>
+        </is>
+      </c>
+      <c r="Q100" t="n">
+        <v>486224</v>
+      </c>
+      <c r="R100" t="n">
+        <v>6565519</v>
+      </c>
+      <c r="S100" t="n">
+        <v>25</v>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>Lekeberg</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W100" t="inlineStr">
+        <is>
+          <t>Knista</t>
+        </is>
+      </c>
+      <c r="Y100" t="inlineStr">
+        <is>
+          <t>2025-01-10</t>
+        </is>
+      </c>
+      <c r="Z100" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>2025-01-10</t>
+        </is>
+      </c>
+      <c r="AB100" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>Spår i snön av tjäder.</t>
+        </is>
+      </c>
+      <c r="AD100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT100" t="inlineStr"/>
+      <c r="AW100" t="inlineStr">
+        <is>
+          <t>Sara Johansson</t>
+        </is>
+      </c>
+      <c r="AX100" t="inlineStr">
+        <is>
+          <t>Sara Johansson</t>
+        </is>
+      </c>
+      <c r="AY100" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 4079-2021 artfynd.xlsx
+++ b/artfynd/A 4079-2021 artfynd.xlsx
@@ -12580,7 +12580,7 @@
         <v>122030502</v>
       </c>
       <c r="B100" t="n">
-        <v>56584</v>
+        <v>56589</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
